--- a/exam_schedule_summer.xlsx
+++ b/exam_schedule_summer.xlsx
@@ -28,17 +28,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Cambria"/>
       <b val="1"/>
-      <sz val="14"/>
+      <sz val="12"/>
     </font>
     <font>
-      <name val="Cambria"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -51,18 +48,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4"/>
-        <bgColor rgb="FF4472C4"/>
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -71,16 +74,16 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -447,17 +450,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -515,22 +518,22 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>26-07-13</t>
+          <t>26-08-10</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>11:30 to 1:30 PM</t>
+          <t>9:00 AM to 12:00 PM</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>MT2005</t>
+          <t>MT1003</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Probability and Satistics</t>
+          <t>Calculus and Analytical Geometry</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -543,9 +546,9 @@
           <t>Summer</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>C-301, C-302</t>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>C-301</t>
         </is>
       </c>
     </row>
@@ -555,22 +558,22 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>26-07-13</t>
+          <t>26-08-10</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>2:00 to 4:00 PM</t>
+          <t>9:00 AM to 12:00 PM</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>EE1005</t>
+          <t>MT1008</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Digital Logic Design</t>
+          <t>Multivariable Calculus</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -583,9 +586,9 @@
           <t>Summer</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>C-301, C-302</t>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>C-302, C-303, C-304</t>
         </is>
       </c>
     </row>
@@ -595,22 +598,22 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>26-07-13</t>
+          <t>26-08-11</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 11:00 AM</t>
+          <t>9:00 AM to 12:00 PM</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>MT1003</t>
+          <t>CS1004</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Calculus and Analytical Geometry</t>
+          <t>Object Oriented Programming</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -623,9 +626,9 @@
           <t>Summer</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>C-301</t>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>C-301, C-302</t>
         </is>
       </c>
     </row>
@@ -635,22 +638,22 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>26-07-13</t>
+          <t>26-08-11</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 11:00 AM</t>
+          <t>9:00 AM to 12:00 PM</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>MT1008</t>
+          <t>AI4009</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Multivariable Calculus</t>
+          <t>Generative AI</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -663,9 +666,9 @@
           <t>Summer</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>C-302, C-303, C-304, C-305</t>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>C-303</t>
         </is>
       </c>
     </row>
@@ -675,22 +678,22 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>26-07-14</t>
+          <t>26-08-11</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>11:30 to 1:30 PM</t>
+          <t>9:00 AM to 12:00 PM</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>MT1004</t>
+          <t>CS1002</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Linear Algebra</t>
+          <t>Programming Fundamental</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -703,9 +706,9 @@
           <t>Summer</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>C-301, C-302, C-303</t>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>C-304</t>
         </is>
       </c>
     </row>
@@ -715,22 +718,22 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>26-07-14</t>
+          <t>26-08-11</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>2:00 to 4:00 PM</t>
+          <t>1:00 PM to 4:00 PM</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>NS1001</t>
+          <t>MT1004</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Applied Physics</t>
+          <t>Linear Algebra</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -743,9 +746,9 @@
           <t>Summer</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>C-301, C-302, C-303, C-304, C-305</t>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>C-301, C-302</t>
         </is>
       </c>
     </row>
@@ -755,22 +758,22 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>26-07-14</t>
+          <t>26-08-11</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 11:00 AM</t>
+          <t>1:00 PM to 4:00 PM</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>CS1004</t>
+          <t>EE1005</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Object Oriented Programming</t>
+          <t>Digital Logic Design</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -783,9 +786,9 @@
           <t>Summer</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>C-301, C-302</t>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>C-303, C-304</t>
         </is>
       </c>
     </row>
@@ -795,22 +798,22 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>26-07-14</t>
+          <t>26-08-12</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 11:00 AM</t>
+          <t>9:00 AM to 12:00 PM</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>AI4009</t>
+          <t>NS1001</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Generative AI</t>
+          <t>Applied Physics</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -823,9 +826,209 @@
           <t>Summer</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>C-301, C-302, C-303, C-304</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>26-08-12</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>1:00 PM to 4:00 PM</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>EL1005</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Digital Logic Design Lab</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Summer</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>C-301, C-302</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>26-08-13</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>9:00 AM to 12:00 PM</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>MT2005</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Probability and Satistics</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Summer</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>C-301, C-302</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>26-08-13</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>1:00 PM to 4:00 PM</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>CL1004</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Object Oriented Programming Lab</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Summer</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>C-301, C-302</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>26-08-13</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>1:00 PM to 4:00 PM</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>CL1002</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Programming Fundamental Lab</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Summer</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>C-303</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>26-08-15</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>9:00 AM to 12:00 PM</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>CS1005</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Discrete Structures</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Summer</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>C-301, C-302</t>
         </is>
       </c>
     </row>
@@ -843,17 +1046,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -911,27 +1114,27 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>26-07-13</t>
+          <t>26-08-10</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>2:00 to 4:00 PM</t>
+          <t>9:00 AM to 12:00 PM</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>MT2004</t>
+          <t>AF1002</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Business Math –II</t>
+          <t>Financial Accounting</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>ALL (BAF-9A)</t>
+          <t>ALL (BAF-9A, 9B)</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -939,9 +1142,9 @@
           <t>Summer</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>A-101  1st flr</t>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>A-101  1st flr, A-102 1st flr</t>
         </is>
       </c>
     </row>
@@ -951,27 +1154,27 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>26-07-13</t>
+          <t>26-08-11</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 11:00 AM</t>
+          <t>9:00 AM to 12:00 PM</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>AF1002</t>
+          <t>MG2008</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Financial Accounting</t>
+          <t>Data Analysis for Business I</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>ALL (BAF-9A, 9B)</t>
+          <t>ALL (BBA-9A)</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -979,9 +1182,9 @@
           <t>Summer</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>A-101  1st flr, A-102 1st flr</t>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>A-101  1st flr</t>
         </is>
       </c>
     </row>
@@ -991,12 +1194,12 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>26-07-14</t>
+          <t>26-08-12</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>2:00 to 4:00 PM</t>
+          <t>9:00 AM to 12:00 PM</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -1019,7 +1222,7 @@
           <t>Summer</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>A-101  1st flr</t>
         </is>
@@ -1031,27 +1234,27 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>26-07-14</t>
+          <t>26-08-12</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 11:00 AM</t>
+          <t>9:00 AM to 12:00 PM</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>MG2008</t>
+          <t>CS4089</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Data Analysis for Business I</t>
+          <t>Programming for Business Applications</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>ALL (BBA-9A)</t>
+          <t>ALL (MSBA-9A)</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1059,7 +1262,127 @@
           <t>Summer</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>A-102 1st flr</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>26-08-13</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>9:00 AM to 12:00 PM</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>MT2004</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Business Math –II</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>ALL (BAF-9A)</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Summer</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>A-101  1st flr</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>26-08-13</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>9:00 AM to 12:00 PM</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>CL2016</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Programming for Business Lab</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>ALL (BFT-09A)</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Summer</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>A-102 1st flr</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>26-08-13</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>1:00 PM to 4:00 PM</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>FL1002</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Financial Accounting  Lab</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>ALL (BAF-9A, 9B)</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Summer</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>A-101  1st flr</t>
         </is>
@@ -1085,11 +1408,11 @@
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1147,12 +1470,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>26-07-13</t>
+          <t>26-08-10</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 11:00 AM</t>
+          <t>9:00 AM to 12:00 PM</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1175,7 +1498,7 @@
           <t>Summer</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>B-019</t>
         </is>
@@ -1187,12 +1510,12 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>26-07-13</t>
+          <t>26-08-10</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 11:00 AM</t>
+          <t>9:00 AM to 12:00 PM</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -1215,7 +1538,7 @@
           <t>Summer</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>B-027, B-028, B-030</t>
         </is>
@@ -1227,27 +1550,27 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>26-07-14</t>
+          <t>26-08-11</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>2:00 to 4:00 PM</t>
+          <t>9:00 AM to 12:00 PM</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>CS1002</t>
+          <t>MT1006</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Programming Fundamentals</t>
+          <t>Differential Equations</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>ALL (A)</t>
+          <t>ALL (AB)</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1255,9 +1578,9 @@
           <t>Summer</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>B-027</t>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>B-027, B-028</t>
         </is>
       </c>
     </row>
@@ -1267,22 +1590,22 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>26-07-14</t>
+          <t>26-08-12</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>2:00 to 4:00 PM</t>
+          <t>9:00 AM to 12:00 PM</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>CS1011</t>
+          <t>CS1002</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Programming for Engineers</t>
+          <t>Programming Fundamentals</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -1295,9 +1618,9 @@
           <t>Summer</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>B-028</t>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>B-027</t>
         </is>
       </c>
     </row>
@@ -1307,27 +1630,27 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>26-07-14</t>
+          <t>26-08-12</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 11:00 AM</t>
+          <t>9:00 AM to 12:00 PM</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>MT2008</t>
+          <t>CS1011</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Multivariable Calculus</t>
+          <t>Programming for Engineers</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>ALL (AB)</t>
+          <t>ALL (A)</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1335,7 +1658,7 @@
           <t>Summer</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>B-027</t>
         </is>
@@ -1347,22 +1670,22 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>26-07-14</t>
+          <t>26-08-12</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 11:00 AM</t>
+          <t>9:00 AM to 12:00 PM</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>MT1006</t>
+          <t>MT2008</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Differential Equations</t>
+          <t>Multivariable Calculus</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1375,9 +1698,9 @@
           <t>Summer</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>B-028, B-030</t>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>B-028</t>
         </is>
       </c>
     </row>
